--- a/reports/pdf_change_20260630.xlsx
+++ b/reports/pdf_change_20260630.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>덕산네오룩스</t>
+          <t>새로닉스</t>
         </is>
       </c>
       <c r="F25" s="14" t="n">
@@ -928,7 +928,7 @@
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>42→14</t>
+          <t>978→950</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>새로닉스</t>
+          <t>덕산네오룩스</t>
         </is>
       </c>
       <c r="F26" s="14" t="n">
@@ -956,7 +956,7 @@
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
-          <t>978→950</t>
+          <t>42→14</t>
         </is>
       </c>
     </row>
@@ -994,7 +994,7 @@
       <c r="C28" s="15" t="n"/>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>코오롱티슈진</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="F28" s="14" t="n">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
-          <t>80→77</t>
+          <t>68→65</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       <c r="C29" s="15" t="n"/>
       <c r="E29" s="13" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>코오롱티슈진</t>
         </is>
       </c>
       <c r="F29" s="14" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>68→65</t>
+          <t>80→77</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_change_20260630.xlsx
+++ b/reports/pdf_change_20260630.xlsx
@@ -907,7 +907,7 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="B25" s="11" t="n">
@@ -915,12 +915,12 @@
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>52→60</t>
+          <t>60→68</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>새로닉스</t>
+          <t>덕산네오룩스</t>
         </is>
       </c>
       <c r="F25" s="14" t="n">
@@ -928,14 +928,14 @@
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>978→950</t>
+          <t>42→14</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B26" s="11" t="n">
@@ -943,12 +943,12 @@
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>60→68</t>
+          <t>52→60</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>덕산네오룩스</t>
+          <t>새로닉스</t>
         </is>
       </c>
       <c r="F26" s="14" t="n">
@@ -956,7 +956,7 @@
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
-          <t>42→14</t>
+          <t>978→950</t>
         </is>
       </c>
     </row>
@@ -994,7 +994,7 @@
       <c r="C28" s="15" t="n"/>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>코오롱티슈진</t>
         </is>
       </c>
       <c r="F28" s="14" t="n">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
-          <t>68→65</t>
+          <t>80→77</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       <c r="C29" s="15" t="n"/>
       <c r="E29" s="13" t="inlineStr">
         <is>
-          <t>코오롱티슈진</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="F29" s="14" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>80→77</t>
+          <t>68→65</t>
         </is>
       </c>
     </row>
